--- a/artfynd/A 50837-2025 artfynd.xlsx
+++ b/artfynd/A 50837-2025 artfynd.xlsx
@@ -2452,7 +2452,7 @@
         <v>131113915</v>
       </c>
       <c r="B18" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50837-2025 artfynd.xlsx
+++ b/artfynd/A 50837-2025 artfynd.xlsx
@@ -2452,7 +2452,7 @@
         <v>131113915</v>
       </c>
       <c r="B18" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50837-2025 artfynd.xlsx
+++ b/artfynd/A 50837-2025 artfynd.xlsx
@@ -2452,7 +2452,7 @@
         <v>131113915</v>
       </c>
       <c r="B18" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50837-2025 artfynd.xlsx
+++ b/artfynd/A 50837-2025 artfynd.xlsx
@@ -2452,7 +2452,7 @@
         <v>131113915</v>
       </c>
       <c r="B18" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50837-2025 artfynd.xlsx
+++ b/artfynd/A 50837-2025 artfynd.xlsx
@@ -2452,7 +2452,7 @@
         <v>131113915</v>
       </c>
       <c r="B18" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 50837-2025 artfynd.xlsx
+++ b/artfynd/A 50837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105734053</v>
+        <v>120460299</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>815841.2075197162</v>
+        <v>816418</v>
       </c>
       <c r="R2" t="n">
-        <v>7376188.397891732</v>
+        <v>7375600</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105734104</v>
+        <v>120460289</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>815890.5628062837</v>
+        <v>816330</v>
       </c>
       <c r="R3" t="n">
-        <v>7376306.952372888</v>
+        <v>7375496</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +861,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105734054</v>
+        <v>120460256</v>
       </c>
       <c r="B4" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>815906.306491558</v>
+        <v>816425</v>
       </c>
       <c r="R4" t="n">
-        <v>7376325.338431715</v>
+        <v>7375615</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,22 +942,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,49 +962,48 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105734020</v>
+        <v>105734084</v>
       </c>
       <c r="B5" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1962</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>815882.8009381397</v>
+        <v>815845</v>
       </c>
       <c r="R5" t="n">
-        <v>7376278.94710584</v>
+        <v>7376231</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1046,9 @@
           <t>2022-09-16</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1075,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105734019</v>
+        <v>65425650</v>
       </c>
       <c r="B6" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,34 +1086,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Trollknabbarna, Nb</t>
+          <t>Dockasberg, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>815834.6465517792</v>
+        <v>816386</v>
       </c>
       <c r="R6" t="n">
-        <v>7376296.149469818</v>
+        <v>7375767</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,22 +1140,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,27 +1165,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105734050</v>
+        <v>65425651</v>
       </c>
       <c r="B7" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,34 +1188,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Trollknabbarna, Nb</t>
+          <t>Dockasberg, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>816394.4386416047</v>
+        <v>816423</v>
       </c>
       <c r="R7" t="n">
-        <v>7375785.647795839</v>
+        <v>7375590</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,22 +1242,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,27 +1267,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>105734103</v>
+        <v>105734019</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1290,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1314,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>815970.448352196</v>
+        <v>815835</v>
       </c>
       <c r="R8" t="n">
-        <v>7376317.240541179</v>
+        <v>7376296</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1347,9 @@
           <t>2022-09-16</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1376,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>105734051</v>
+        <v>105734020</v>
       </c>
       <c r="B9" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1475,21 +1387,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1411,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>815721.7042633251</v>
+        <v>815883</v>
       </c>
       <c r="R9" t="n">
-        <v>7376312.879684517</v>
+        <v>7376279</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1444,9 @@
           <t>2022-09-16</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,37 +1473,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>105734105</v>
+        <v>120460401</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1508,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>815895.4380723546</v>
+        <v>816332</v>
       </c>
       <c r="R10" t="n">
-        <v>7376313.983340234</v>
+        <v>7375499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,22 +1538,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,62 +1558,61 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>105734084</v>
+        <v>65426309</v>
       </c>
       <c r="B11" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Trollknabbarna, Nb</t>
+          <t>Dockasberg, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>815845.7358390717</v>
+        <v>816385</v>
       </c>
       <c r="R11" t="n">
-        <v>7376230.610868695</v>
+        <v>7375742</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,22 +1639,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-26</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-10-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1783,49 +1664,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>105734068</v>
+        <v>105734103</v>
       </c>
       <c r="B12" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1711,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>816624.5008370234</v>
+        <v>815970</v>
       </c>
       <c r="R12" t="n">
-        <v>7375776.592274587</v>
+        <v>7376317</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1744,9 @@
           <t>2022-09-16</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1773,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>105734080</v>
+        <v>105734104</v>
       </c>
       <c r="B13" t="n">
-        <v>95522</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221946</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1808,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>816515.6669834671</v>
+        <v>815891</v>
       </c>
       <c r="R13" t="n">
-        <v>7375846.0030262</v>
+        <v>7376307</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1841,9 @@
           <t>2022-09-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,37 +1870,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>105734069</v>
+        <v>105734105</v>
       </c>
       <c r="B14" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1905,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>815896.6754429957</v>
+        <v>815895</v>
       </c>
       <c r="R14" t="n">
-        <v>7376221.011492592</v>
+        <v>7376314</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,19 +1938,9 @@
           <t>2022-09-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-09-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,37 +1967,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120460384</v>
+        <v>120460343</v>
       </c>
       <c r="B15" t="n">
-        <v>97957</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +2002,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>816183</v>
+        <v>816383</v>
       </c>
       <c r="R15" t="n">
-        <v>7375924</v>
+        <v>7375619</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2237,37 +2068,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120460312</v>
+        <v>120460400</v>
       </c>
       <c r="B16" t="n">
-        <v>97944</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220093</v>
+        <v>6487</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2277,10 +2103,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>816276</v>
+        <v>816176</v>
       </c>
       <c r="R16" t="n">
-        <v>7375718</v>
+        <v>7375908</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2343,37 +2169,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120460343</v>
+        <v>105734050</v>
       </c>
       <c r="B17" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2383,10 +2204,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>816383</v>
+        <v>816394</v>
       </c>
       <c r="R17" t="n">
-        <v>7375619</v>
+        <v>7375786</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2413,12 +2234,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2433,30 +2254,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Torbjörn Josefsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131113915</v>
+        <v>105734051</v>
       </c>
       <c r="B18" t="n">
-        <v>57889</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2477,36 +2294,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Trollknabbarna, Dockasberg, Nb</t>
+          <t>Trollknabbarna, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>816315</v>
+        <v>815721</v>
       </c>
       <c r="R18" t="n">
-        <v>7375643</v>
+        <v>7376313</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2530,22 +2331,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>10:02</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>10:05</t>
+          <t>2022-09-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2560,15 +2351,1453 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>105734053</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Trollknabbarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>815841</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7376188</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>105734054</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Trollknabbarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>815906</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7376325</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131113915</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Trollknabbarna, Dockasberg, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>816315</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7375643</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
           <t>Markus  Kristoffersson</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX21" t="inlineStr">
         <is>
           <t>Markus  Kristoffersson</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>105734026</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Trollknabbarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>816386</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7375770</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120460324</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Trollknabbarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>816418</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7375565</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>101693715</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Simonstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>815909</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7376446</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120460255</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Trollknabbarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>816249</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7375502</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120460382</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Trollknabbarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>816263</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7375736</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120460383</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Trollknabbarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>816258</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7375806</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120460384</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Trollknabbarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>816183</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7375924</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120460312</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99022</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Trollknabbarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>816276</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7375718</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-06-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>105734068</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Trollknabbarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>816624</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7375777</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>105734069</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Trollknabbarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>815896</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7376221</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>105734080</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Trollknabbarna, Nb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>816515</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7375846</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Överkalix</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-09-16</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50837-2025 artfynd.xlsx
+++ b/artfynd/A 50837-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460299</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460289</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460256</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105734084</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,6 +1199,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65425650</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1276,6 +1306,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65425651</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1373,6 +1408,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105734019</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1470,6 +1510,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105734020</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1571,6 +1616,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460401</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1673,6 +1723,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65426309</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1770,6 +1825,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105734103</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1867,6 +1927,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105734104</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1964,6 +2029,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105734105</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2065,6 +2135,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460343</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2166,6 +2241,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460400</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2263,6 +2343,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105734050</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2360,6 +2445,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105734051</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2457,6 +2547,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105734053</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2554,6 +2649,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105734054</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2677,6 +2777,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131113915</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2774,6 +2879,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105734026</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2875,6 +2985,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460324</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2988,6 +3103,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101693715</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3103,6 +3223,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460255</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3204,6 +3329,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460382</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3305,6 +3435,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460383</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3406,6 +3541,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460384</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3507,6 +3647,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120460312</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3604,6 +3749,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105734068</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3701,6 +3851,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105734069</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3798,8 +3953,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105734080</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>